--- a/GameConfig/Datas/Defines/__tables__.xlsx
+++ b/GameConfig/Datas/Defines/__tables__.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub Project\DGame_Fantasy\GameConfig\Datas\Defines\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EAA2991-B97B-48E7-ABBF-9D386A97DCCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="68">
   <si>
     <t>##var</t>
   </si>
@@ -122,6 +116,9 @@
     <t>TextConfig</t>
   </si>
   <si>
+    <t>通用配置表/文本配置表.xlsx</t>
+  </si>
+  <si>
     <t>文本配置表</t>
   </si>
   <si>
@@ -131,15 +128,33 @@
     <t>ItemConfig</t>
   </si>
   <si>
+    <t>道具/道具配置表.xlsx</t>
+  </si>
+  <si>
     <t>道具配置表</t>
   </si>
   <si>
+    <t>TbGetWayConfig</t>
+  </si>
+  <si>
+    <t>GetWayConfig</t>
+  </si>
+  <si>
+    <t>道具/获取途径配置表@道具配置表.xlsx</t>
+  </si>
+  <si>
+    <t>获取途径配置表</t>
+  </si>
+  <si>
     <t>TbSoundConfig</t>
   </si>
   <si>
     <t>SoundConfig</t>
   </si>
   <si>
+    <t>通用配置表/音效配置表.xlsx</t>
+  </si>
+  <si>
     <t>音效配置表</t>
   </si>
   <si>
@@ -149,6 +164,9 @@
     <t>ModelConfig</t>
   </si>
   <si>
+    <t>通用配置表/模型配置表.xlsx</t>
+  </si>
+  <si>
     <t>模型配置表</t>
   </si>
   <si>
@@ -158,6 +176,9 @@
     <t>EffectConfig</t>
   </si>
   <si>
+    <t>通用配置表/特效配置表.xlsx</t>
+  </si>
+  <si>
     <t>特效配置表</t>
   </si>
   <si>
@@ -167,6 +188,9 @@
     <t>GmConfig</t>
   </si>
   <si>
+    <t>通用配置表/GM配置表.xlsx</t>
+  </si>
+  <si>
     <t>GM配置表</t>
   </si>
   <si>
@@ -182,63 +206,44 @@
     <t>服务器状态配置表</t>
   </si>
   <si>
-    <t>通用配置表/文本配置表.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>通用配置表/音效配置表.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>通用配置表/模型配置表.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>通用配置表/特效配置表.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>通用配置表/GM配置表.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>TbGetWayConfig</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>GetWayConfig</t>
-  </si>
-  <si>
-    <t>获取途径配置表</t>
-  </si>
-  <si>
     <t>TbFuncOpenConfig</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>FuncOpenConfig</t>
   </si>
   <si>
     <t>通用配置表/系统开放配置表.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>系统开放配置表</t>
   </si>
   <si>
-    <t>道具/道具配置表.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>道具/获取途径配置表@道具配置表.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>TbFuncParamConfig</t>
+  </si>
+  <si>
+    <t>FuncParamConfig</t>
+  </si>
+  <si>
+    <t>通用配置表/功能参数配置表.xlsx</t>
+  </si>
+  <si>
+    <t>one</t>
+  </si>
+  <si>
+    <t>功能参数配置表</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -261,22 +266,144 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -289,8 +416,188 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -298,12 +605,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -311,31 +857,74 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="好" xfId="1" builtinId="26"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -593,28 +1182,30 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="20.4140625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="15.58203125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="53.25" style="2" customWidth="1"/>
-    <col min="5" max="6" width="50.9140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="55.75" style="2" customWidth="1"/>
-    <col min="8" max="8" width="39.9140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="25.125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="50.125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="50.9166666666667" style="2" customWidth="1"/>
+    <col min="6" max="6" width="84.25" style="2" customWidth="1"/>
+    <col min="7" max="7" width="31.5" style="2" customWidth="1"/>
+    <col min="8" max="8" width="55.25" style="2" customWidth="1"/>
     <col min="9" max="9" width="18" style="2" customWidth="1"/>
     <col min="10" max="10" width="28.75" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="2"/>
+    <col min="11" max="11" width="34.25" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" s="1" customFormat="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -649,7 +1240,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" s="1" customFormat="1" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -681,7 +1272,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" s="1" customFormat="1" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -704,7 +1295,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11">
       <c r="B4" s="3" t="s">
         <v>27</v>
       </c>
@@ -715,103 +1306,103 @@
         <v>1</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11">
       <c r="B5" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11">
       <c r="B6" s="4" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="D6" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11">
       <c r="B7" s="2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D7" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11">
       <c r="B8" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D8" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11">
       <c r="B9" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D9" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E9" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="B10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="D10" s="2" t="b">
         <v>1</v>
@@ -820,57 +1411,77 @@
         <v>53</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11">
       <c r="B11" s="3" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D11" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="2" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11">
       <c r="B12" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D12" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="B13" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D13 D4:D12 D14:D1048576">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/GameConfig/Datas/Defines/__tables__.xlsx
+++ b/GameConfig/Datas/Defines/__tables__.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub Project\DGame_Fantasy\GameConfig\Datas\Defines\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B70DABBA-DB5A-48D5-B0BB-A9FD0BCE1CCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="72">
   <si>
     <t>##var</t>
   </si>
@@ -218,32 +224,41 @@
     <t>系统开放配置表</t>
   </si>
   <si>
+    <t>通用配置表/功能参数配置表.xlsx</t>
+  </si>
+  <si>
+    <t>one</t>
+  </si>
+  <si>
+    <t>功能参数配置表</t>
+  </si>
+  <si>
+    <t>运营/活动开启配置表.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动开启配置表</t>
+  </si>
+  <si>
+    <t>TbActivityOpenConfig</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActivityOpenConfig</t>
+  </si>
+  <si>
     <t>TbFuncParamConfig</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>FuncParamConfig</t>
-  </si>
-  <si>
-    <t>通用配置表/功能参数配置表.xlsx</t>
-  </si>
-  <si>
-    <t>one</t>
-  </si>
-  <si>
-    <t>功能参数配置表</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -255,6 +270,7 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -262,148 +278,19 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -416,188 +303,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -605,251 +312,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -857,7 +325,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -870,61 +338,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="好" xfId="1" builtinId="26"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1182,20 +607,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="26.875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="25.125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="50.125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="50.9166666666667" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="25.08203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="50.08203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="50.9140625" style="2" customWidth="1"/>
     <col min="6" max="6" width="84.25" style="2" customWidth="1"/>
     <col min="7" max="7" width="31.5" style="2" customWidth="1"/>
     <col min="8" max="8" width="55.25" style="2" customWidth="1"/>
@@ -1205,7 +630,7 @@
     <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:11">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1240,7 +665,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:11">
+    <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -1272,7 +697,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:11">
+    <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1295,7 +720,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>27</v>
       </c>
@@ -1312,7 +737,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>31</v>
       </c>
@@ -1329,7 +754,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>35</v>
       </c>
@@ -1346,7 +771,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
         <v>39</v>
       </c>
@@ -1363,7 +788,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
         <v>43</v>
       </c>
@@ -1380,7 +805,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
         <v>47</v>
       </c>
@@ -1397,7 +822,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
         <v>51</v>
       </c>
@@ -1414,7 +839,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
         <v>55</v>
       </c>
@@ -1434,7 +859,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>59</v>
       </c>
@@ -1454,34 +879,51 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="G13" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" s="4" t="s">
+      <c r="I13" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G13" s="2" t="s">
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B14" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="I14" s="2" t="s">
         <v>67</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D13 D4:D12 D14:D1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/GameConfig/Datas/Defines/__tables__.xlsx
+++ b/GameConfig/Datas/Defines/__tables__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub Project\DGame_Fantasy\GameConfig\Datas\Defines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B70DABBA-DB5A-48D5-B0BB-A9FD0BCE1CCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6628009-F14F-4CD7-887B-C972CBE6F82F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="73">
   <si>
     <t>##var</t>
   </si>
@@ -252,6 +252,10 @@
   </si>
   <si>
     <t>FuncParamConfig</t>
+  </si>
+  <si>
+    <t>s</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -912,6 +916,9 @@
       <c r="E14" s="4" t="s">
         <v>66</v>
       </c>
+      <c r="H14" s="4" t="s">
+        <v>72</v>
+      </c>
       <c r="I14" s="2" t="s">
         <v>67</v>
       </c>

--- a/GameConfig/Datas/Defines/__tables__.xlsx
+++ b/GameConfig/Datas/Defines/__tables__.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub Project\DGame_Fantasy\GameConfig\Datas\Defines\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6628009-F14F-4CD7-887B-C972CBE6F82F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="77">
   <si>
     <t>##var</t>
   </si>
@@ -140,6 +134,18 @@
     <t>道具配置表</t>
   </si>
   <si>
+    <t>TbCurrencyConfig</t>
+  </si>
+  <si>
+    <t>CurrencyConfig</t>
+  </si>
+  <si>
+    <t>道具/货币配置表@道具配置表.xlsx</t>
+  </si>
+  <si>
+    <t>货币配置表</t>
+  </si>
+  <si>
     <t>TbGetWayConfig</t>
   </si>
   <si>
@@ -224,6 +230,12 @@
     <t>系统开放配置表</t>
   </si>
   <si>
+    <t>TbFuncParamConfig</t>
+  </si>
+  <si>
+    <t>FuncParamConfig</t>
+  </si>
+  <si>
     <t>通用配置表/功能参数配置表.xlsx</t>
   </si>
   <si>
@@ -233,36 +245,32 @@
     <t>功能参数配置表</t>
   </si>
   <si>
+    <t>TbActivityOpenConfig</t>
+  </si>
+  <si>
+    <t>ActivityOpenConfig</t>
+  </si>
+  <si>
     <t>运营/活动开启配置表.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>s</t>
   </si>
   <si>
     <t>活动开启配置表</t>
-  </si>
-  <si>
-    <t>TbActivityOpenConfig</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActivityOpenConfig</t>
-  </si>
-  <si>
-    <t>TbFuncParamConfig</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>FuncParamConfig</t>
-  </si>
-  <si>
-    <t>s</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -274,27 +282,148 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -307,8 +436,188 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -316,20 +625,259 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -338,22 +886,62 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="好" xfId="1" builtinId="26"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -611,20 +1199,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="26.83203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="25.08203125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="50.08203125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="50.9140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.8333333333333" style="2" customWidth="1"/>
+    <col min="3" max="3" width="25.0833333333333" style="2" customWidth="1"/>
+    <col min="4" max="4" width="50.0833333333333" style="2" customWidth="1"/>
+    <col min="5" max="5" width="50.9166666666667" style="2" customWidth="1"/>
     <col min="6" max="6" width="84.25" style="2" customWidth="1"/>
     <col min="7" max="7" width="31.5" style="2" customWidth="1"/>
     <col min="8" max="8" width="55.25" style="2" customWidth="1"/>
@@ -634,7 +1222,7 @@
     <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" s="1" customFormat="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -669,7 +1257,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" s="1" customFormat="1" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -701,7 +1289,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" s="1" customFormat="1" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -724,7 +1312,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11">
       <c r="B4" s="3" t="s">
         <v>27</v>
       </c>
@@ -734,14 +1322,14 @@
       <c r="D4" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>29</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11">
       <c r="B5" s="2" t="s">
         <v>31</v>
       </c>
@@ -751,18 +1339,21 @@
       <c r="D5" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B6" s="4" t="s">
+    <row r="6" spans="1:11">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D6" s="2" t="b">
@@ -771,12 +1362,13 @@
       <c r="E6" s="2" t="s">
         <v>37</v>
       </c>
+      <c r="H6" s="3"/>
       <c r="I6" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B7" s="2" t="s">
+    <row r="7" spans="1:11">
+      <c r="B7" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -785,14 +1377,14 @@
       <c r="D7" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="2" t="s">
         <v>41</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11">
       <c r="B8" s="2" t="s">
         <v>43</v>
       </c>
@@ -802,14 +1394,14 @@
       <c r="D8" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>45</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11">
       <c r="B9" s="2" t="s">
         <v>47</v>
       </c>
@@ -819,14 +1411,14 @@
       <c r="D9" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>49</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11">
       <c r="B10" s="2" t="s">
         <v>51</v>
       </c>
@@ -836,15 +1428,15 @@
       <c r="D10" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>53</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B11" s="3" t="s">
+    <row r="11" spans="1:11">
+      <c r="B11" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -856,15 +1448,12 @@
       <c r="E11" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
       <c r="I11" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B12" s="4" t="s">
+    <row r="12" spans="1:11">
+      <c r="B12" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -873,7 +1462,7 @@
       <c r="D12" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>61</v>
       </c>
       <c r="F12" s="3"/>
@@ -883,54 +1472,74 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B13" s="4" t="s">
-        <v>70</v>
+    <row r="13" spans="1:11">
+      <c r="B13" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D13" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>64</v>
-      </c>
+      <c r="E13" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
       <c r="I13" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B14" s="4" t="s">
+    <row r="14" spans="1:11">
+      <c r="B14" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="D14" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H14" s="4" t="s">
+      <c r="E14" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="B15" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="I14" s="2" t="s">
-        <v>67</v>
+      <c r="C15" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D15 D17:D1048576">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/GameConfig/Datas/Defines/__tables__.xlsx
+++ b/GameConfig/Datas/Defines/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="77">
   <si>
     <t>##var</t>
   </si>
@@ -128,7 +128,7 @@
     <t>ItemConfig</t>
   </si>
   <si>
-    <t>道具/道具配置表.xlsx</t>
+    <t>道具配置表@道具/道具配置表.xlsx</t>
   </si>
   <si>
     <t>道具配置表</t>
@@ -140,7 +140,7 @@
     <t>CurrencyConfig</t>
   </si>
   <si>
-    <t>道具/货币配置表@道具配置表.xlsx</t>
+    <t>货币配置表@道具/道具配置表.xlsx</t>
   </si>
   <si>
     <t>货币配置表</t>
@@ -152,7 +152,7 @@
     <t>GetWayConfig</t>
   </si>
   <si>
-    <t>道具/获取途径配置表@道具配置表.xlsx</t>
+    <t>获取途径配置表@道具/道具配置表.xlsx</t>
   </si>
   <si>
     <t>获取途径配置表</t>
@@ -1347,9 +1347,6 @@
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="B6" s="3" t="s">
         <v>35</v>
       </c>

--- a/GameConfig/Datas/Defines/__tables__.xlsx
+++ b/GameConfig/Datas/Defines/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub Project\DGame_Fantasy\GameConfig\Datas\Defines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD6D0914-0439-4CFC-A104-B8EE5B404887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A48201EB-FA25-4EB5-8362-D562098D30D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60765" yWindow="3555" windowWidth="33795" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="60105" yWindow="5265" windowWidth="33795" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="83">
   <si>
     <t>##var</t>
   </si>
@@ -273,19 +273,27 @@
     <t>服务器配置表</t>
   </si>
   <si>
-    <t>服务器配置表@通用/服务器配置表.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>服务器状态配置表@通用/服务器配置表.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>TbServerConfig</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>ServerConfig</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>服务器配置表@运营/服务器配置表.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>服务器状态配置表@运营/服务器配置表.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>##</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>运营相关</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -650,7 +658,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -896,102 +904,115 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D12" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>78</v>
+      <c r="E12" s="4" t="s">
+        <v>74</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D13" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
+        <v>75</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="I13" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B14" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D14" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>63</v>
+      <c r="A14" s="4" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B15" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D15" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>68</v>
+      <c r="A15" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>79</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D16" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>77</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>67</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B17" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B18" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/GameConfig/Datas/Defines/__tables__.xlsx
+++ b/GameConfig/Datas/Defines/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub Project\DGame_Fantasy\GameConfig\Datas\Defines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A48201EB-FA25-4EB5-8362-D562098D30D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{312148C9-8022-4644-B6AE-DF64790E25F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60105" yWindow="5265" windowWidth="33795" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="87">
   <si>
     <t>##var</t>
   </si>
@@ -295,6 +295,18 @@
   <si>
     <t>运营相关</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbPlayerInitConfig</t>
+  </si>
+  <si>
+    <t>PlayerInitConfig</t>
+  </si>
+  <si>
+    <t>运营/角色初始配置表.xlsx</t>
+  </si>
+  <si>
+    <t>角色初始配置表</t>
   </si>
 </sst>
 </file>
@@ -658,7 +670,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -1015,6 +1027,26 @@
         <v>68</v>
       </c>
     </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B19" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D19" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">

--- a/GameConfig/Datas/Defines/__tables__.xlsx
+++ b/GameConfig/Datas/Defines/__tables__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub Project\DGame_Fantasy\GameConfig\Datas\Defines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{312148C9-8022-4644-B6AE-DF64790E25F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11091E69-38F9-4519-B110-3FEBC463A2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="91">
   <si>
     <t>##var</t>
   </si>
@@ -307,6 +307,21 @@
   </si>
   <si>
     <t>角色初始配置表</t>
+  </si>
+  <si>
+    <t>运营/随机名配置表.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>随机名配置表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbRandomNameConfig</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RandomNameConfig</t>
   </si>
 </sst>
 </file>
@@ -325,6 +340,7 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -670,7 +686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -1047,6 +1063,26 @@
         <v>86</v>
       </c>
     </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B20" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">

--- a/GameConfig/Datas/Defines/__tables__.xlsx
+++ b/GameConfig/Datas/Defines/__tables__.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub Project\DGame_Fantasy\GameConfig\Datas\Defines\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub_Project\DGame_Fantasy\GameConfig\Datas\Defines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11091E69-38F9-4519-B110-3FEBC463A2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9E54420-994B-4150-AFD6-041DF89A6FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="95">
   <si>
     <t>##var</t>
   </si>
@@ -250,10 +250,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>通用/模型配置表.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>通用/音效配置表.xlsx</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -322,6 +318,25 @@
   </si>
   <si>
     <t>RandomNameConfig</t>
+  </si>
+  <si>
+    <t>模型/模型配置表.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbWeaponModelConfig</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeaponModelConfig</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>模型/武器模型配置表.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器模型配置表</t>
   </si>
 </sst>
 </file>
@@ -686,7 +701,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -804,7 +819,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>29</v>
@@ -873,7 +888,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>44</v>
@@ -890,197 +905,214 @@
         <v>1</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>49</v>
+      <c r="B10" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>92</v>
       </c>
       <c r="D10" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D11" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" s="4" t="s">
+      <c r="D12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="I12" s="2" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B12" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D12" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B14" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D13" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="G13" s="2" t="s">
+      <c r="D14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="I14" s="2" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B16" s="4" t="s">
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B17" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="D17" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="D16" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="H16" s="3" t="s">
+      <c r="H17" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="I16" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B17" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
       <c r="I17" s="2" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B19" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D18" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="3" t="s">
+      <c r="D19" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="H19" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="I18" s="2" t="s">
+      <c r="I19" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B19" s="2" t="s">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B20" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D20" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="D19" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B20" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D20" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>87</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="I20" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B21" s="4" t="s">
         <v>88</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D21" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/GameConfig/Datas/Defines/__tables__.xlsx
+++ b/GameConfig/Datas/Defines/__tables__.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub_Project\DGame_Fantasy\GameConfig\Datas\Defines\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9E54420-994B-4150-AFD6-041DF89A6FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="98">
   <si>
     <t>##var</t>
   </si>
@@ -122,6 +116,9 @@
     <t>TextConfig</t>
   </si>
   <si>
+    <t>通用/文本配置表.xlsx</t>
+  </si>
+  <si>
     <t>文本配置表</t>
   </si>
   <si>
@@ -167,6 +164,9 @@
     <t>SoundConfig</t>
   </si>
   <si>
+    <t>通用/音效配置表.xlsx</t>
+  </si>
+  <si>
     <t>音效配置表</t>
   </si>
   <si>
@@ -176,15 +176,33 @@
     <t>ModelConfig</t>
   </si>
   <si>
+    <t>模型/模型配置表.xlsx</t>
+  </si>
+  <si>
     <t>模型配置表</t>
   </si>
   <si>
+    <t>TbWeaponModelConfig</t>
+  </si>
+  <si>
+    <t>WeaponModelConfig</t>
+  </si>
+  <si>
+    <t>模型/武器模型配置表.xlsx</t>
+  </si>
+  <si>
+    <t>武器模型配置表</t>
+  </si>
+  <si>
     <t>TbEffectConfig</t>
   </si>
   <si>
     <t>EffectConfig</t>
   </si>
   <si>
+    <t>通用/特效配置表.xlsx</t>
+  </si>
+  <si>
     <t>特效配置表</t>
   </si>
   <si>
@@ -194,39 +212,81 @@
     <t>GmConfig</t>
   </si>
   <si>
+    <t>通用/GM配置表.xlsx</t>
+  </si>
+  <si>
     <t>GM配置表</t>
   </si>
   <si>
+    <t>TbFuncOpenConfig</t>
+  </si>
+  <si>
+    <t>FuncOpenConfig</t>
+  </si>
+  <si>
+    <t>通用/系统开放配置表.xlsx</t>
+  </si>
+  <si>
+    <t>系统开放配置表</t>
+  </si>
+  <si>
+    <t>TbFuncParamConfig</t>
+  </si>
+  <si>
+    <t>FuncParamConfig</t>
+  </si>
+  <si>
+    <t>通用/功能参数配置表.xlsx</t>
+  </si>
+  <si>
+    <t>one</t>
+  </si>
+  <si>
+    <t>功能参数配置表</t>
+  </si>
+  <si>
+    <t>TbChapterConfig</t>
+  </si>
+  <si>
+    <t>ChapterConfig</t>
+  </si>
+  <si>
+    <t>关卡/章节配置表.xlsx</t>
+  </si>
+  <si>
+    <t>章节配置表</t>
+  </si>
+  <si>
+    <t>运营相关</t>
+  </si>
+  <si>
+    <t>TbServerConfig</t>
+  </si>
+  <si>
+    <t>ServerConfig</t>
+  </si>
+  <si>
+    <t>服务器配置表@运营/服务器配置表.xlsx</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>服务器配置表</t>
+  </si>
+  <si>
     <t>TbServerStateConfig</t>
   </si>
   <si>
     <t>ServerStateConfig</t>
   </si>
   <si>
+    <t>服务器状态配置表@运营/服务器配置表.xlsx</t>
+  </si>
+  <si>
     <t>服务器状态配置表</t>
   </si>
   <si>
-    <t>TbFuncOpenConfig</t>
-  </si>
-  <si>
-    <t>FuncOpenConfig</t>
-  </si>
-  <si>
-    <t>系统开放配置表</t>
-  </si>
-  <si>
-    <t>TbFuncParamConfig</t>
-  </si>
-  <si>
-    <t>FuncParamConfig</t>
-  </si>
-  <si>
-    <t>one</t>
-  </si>
-  <si>
-    <t>功能参数配置表</t>
-  </si>
-  <si>
     <t>TbActivityOpenConfig</t>
   </si>
   <si>
@@ -236,63 +296,9 @@
     <t>运营/活动开启配置表.xlsx</t>
   </si>
   <si>
-    <t>s</t>
-  </si>
-  <si>
     <t>活动开启配置表</t>
   </si>
   <si>
-    <t>通用/GM配置表.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>通用/特效配置表.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>通用/音效配置表.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>通用/文本配置表.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>通用/系统开放配置表.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>通用/功能参数配置表.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>服务器配置表</t>
-  </si>
-  <si>
-    <t>TbServerConfig</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ServerConfig</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>服务器配置表@运营/服务器配置表.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>服务器状态配置表@运营/服务器配置表.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>##</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>运营相关</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>TbPlayerInitConfig</t>
   </si>
   <si>
@@ -305,45 +311,29 @@
     <t>角色初始配置表</t>
   </si>
   <si>
+    <t>TbRandomNameConfig</t>
+  </si>
+  <si>
+    <t>RandomNameConfig</t>
+  </si>
+  <si>
     <t>运营/随机名配置表.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>随机名配置表</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>TbRandomNameConfig</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>RandomNameConfig</t>
-  </si>
-  <si>
-    <t>模型/模型配置表.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>TbWeaponModelConfig</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>WeaponModelConfig</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>模型/武器模型配置表.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器模型配置表</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -355,14 +345,6 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -370,12 +352,148 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -388,8 +506,188 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -397,12 +695,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -410,7 +947,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -419,25 +956,68 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="好" xfId="1" builtinId="26"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -695,20 +1275,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="26.83203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="25.08203125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="50.08203125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="50.9140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.8333333333333" style="2" customWidth="1"/>
+    <col min="3" max="3" width="25.0833333333333" style="2" customWidth="1"/>
+    <col min="4" max="4" width="50.0833333333333" style="2" customWidth="1"/>
+    <col min="5" max="5" width="50.9166666666667" style="2" customWidth="1"/>
     <col min="6" max="6" width="84.25" style="2" customWidth="1"/>
     <col min="7" max="7" width="31.5" style="2" customWidth="1"/>
     <col min="8" max="8" width="55.25" style="2" customWidth="1"/>
@@ -718,7 +1298,7 @@
     <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" s="1" customFormat="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -753,7 +1333,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" s="1" customFormat="1" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -785,7 +1365,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" s="1" customFormat="1" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -808,7 +1388,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11">
       <c r="B4" s="3" t="s">
         <v>27</v>
       </c>
@@ -819,228 +1399,225 @@
         <v>1</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="B5" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="B6" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="B7" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D7" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="B8" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D8" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="B9" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D9" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="B10" s="4" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="D10" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="B11" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D11" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="B12" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D12" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="B13" s="3" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D13" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="B14" s="3" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D14" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E14" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="B15" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="G14" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="I15" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="B17" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C17" s="4" t="s">
+    </row>
+    <row r="18" spans="1:9">
+      <c r="B18" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D17" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>78</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B18" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="D18" s="2" t="b">
         <v>1</v>
@@ -1048,81 +1625,101 @@
       <c r="E18" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
+      <c r="H18" s="3" t="s">
+        <v>80</v>
+      </c>
       <c r="I18" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="B19" s="3" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="D19" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>67</v>
-      </c>
+      <c r="E19" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
       <c r="I19" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B20" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="B20" s="3" t="s">
+        <v>86</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D20" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>67</v>
+      <c r="E20" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B21" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="B21" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D21" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>86</v>
+      <c r="E21" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="B22" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D15 D4:D14 D16:D1048576">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/GameConfig/Datas/Defines/__tables__.xlsx
+++ b/GameConfig/Datas/Defines/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="110">
   <si>
     <t>##var</t>
   </si>
@@ -255,6 +255,42 @@
   </si>
   <si>
     <t>章节配置表</t>
+  </si>
+  <si>
+    <t>TbMonsterConfig</t>
+  </si>
+  <si>
+    <t>MonsterConfig</t>
+  </si>
+  <si>
+    <t>关卡/怪物配置表.xlsx</t>
+  </si>
+  <si>
+    <t>怪物配置表</t>
+  </si>
+  <si>
+    <t>TbMapConfig</t>
+  </si>
+  <si>
+    <t>MapConfig</t>
+  </si>
+  <si>
+    <t>地图配置表@关卡/地图相关配置表.xlsx</t>
+  </si>
+  <si>
+    <t>地图配置表</t>
+  </si>
+  <si>
+    <t>TbPathConfig</t>
+  </si>
+  <si>
+    <t>PathConfig</t>
+  </si>
+  <si>
+    <t>路径点配置表@关卡/地图相关配置表.xlsx</t>
+  </si>
+  <si>
+    <t>路径点配置表</t>
   </si>
   <si>
     <t>运营相关</t>
@@ -333,7 +369,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -344,13 +380,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -813,137 +842,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -954,9 +983,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1281,7 +1307,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -1398,7 +1424,7 @@
       <c r="D4" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>29</v>
       </c>
       <c r="I4" s="3" t="s">
@@ -1467,7 +1493,7 @@
       <c r="D8" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>45</v>
       </c>
       <c r="I8" s="2" t="s">
@@ -1484,7 +1510,7 @@
       <c r="D9" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>49</v>
       </c>
       <c r="I9" s="2" t="s">
@@ -1492,16 +1518,16 @@
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D10" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>53</v>
       </c>
       <c r="I10" s="2" t="s">
@@ -1518,7 +1544,7 @@
       <c r="D11" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>57</v>
       </c>
       <c r="I11" s="2" t="s">
@@ -1535,7 +1561,7 @@
       <c r="D12" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>61</v>
       </c>
       <c r="I12" s="2" t="s">
@@ -1552,7 +1578,7 @@
       <c r="D13" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>65</v>
       </c>
       <c r="F13" s="3"/>
@@ -1572,7 +1598,7 @@
       <c r="D14" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
@@ -1592,7 +1618,7 @@
       <c r="D15" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="3" t="s">
         <v>74</v>
       </c>
       <c r="I15" s="2" t="s">
@@ -1600,100 +1626,91 @@
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="4" t="s">
+      <c r="B16" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="B17" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="B18" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="4" t="s">
+    <row r="20" spans="1:9">
+      <c r="A20" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="B18" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D18" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="B19" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D19" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
       <c r="B20" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D20" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="I20" s="2" t="s">
+    </row>
+    <row r="21" spans="1:9">
+      <c r="B21" s="3" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="B21" s="2" t="s">
+      <c r="C21" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D21" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="H21" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>80</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="3" t="s">
         <v>94</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -1705,16 +1722,76 @@
       <c r="E22" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="H22" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="I22" s="4" t="s">
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="2" t="s">
         <v>97</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="B23" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D23" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="B24" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="B25" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D25" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D15 D4:D14 D16:D1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D16 D17 D18 D4:D15 D19:D1048576">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>

--- a/GameConfig/Datas/Defines/__tables__.xlsx
+++ b/GameConfig/Datas/Defines/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="111">
   <si>
     <t>##var</t>
   </si>
@@ -291,6 +291,9 @@
   </si>
   <si>
     <t>路径点配置表</t>
+  </si>
+  <si>
+    <t>group_by:GroupID</t>
   </si>
   <si>
     <t>运营相关</t>
@@ -1642,7 +1645,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:10">
       <c r="B17" s="3" t="s">
         <v>80</v>
       </c>
@@ -1659,7 +1662,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:10">
       <c r="B18" s="3" t="s">
         <v>84</v>
       </c>
@@ -1675,123 +1678,126 @@
       <c r="I18" s="2" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="19" spans="1:9">
+      <c r="J18" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:10">
       <c r="A20" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="B21" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D21" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="B22" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D22" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="B23" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D23" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="B24" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D24" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="B25" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D25" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D16 D17 D18 D4:D15 D19:D1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D1048576">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>

--- a/GameConfig/Datas/Defines/__tables__.xlsx
+++ b/GameConfig/Datas/Defines/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="121">
   <si>
     <t>##var</t>
   </si>
@@ -294,6 +294,36 @@
   </si>
   <si>
     <t>group_by:GroupID</t>
+  </si>
+  <si>
+    <t>TbPlayerModelPairConfig</t>
+  </si>
+  <si>
+    <t>PlayerModelPairConfig</t>
+  </si>
+  <si>
+    <t>角色模型配对表@模型/角色模型配对表.xlsx</t>
+  </si>
+  <si>
+    <t>RoleBodyType+ClothID</t>
+  </si>
+  <si>
+    <t>list</t>
+  </si>
+  <si>
+    <t>角色模型配对表</t>
+  </si>
+  <si>
+    <t>TbPlayerWeaponPairConfig</t>
+  </si>
+  <si>
+    <t>PlayerWeaponPairConfig</t>
+  </si>
+  <si>
+    <t>武器模型配对表@模型/角色模型配对表.xlsx</t>
+  </si>
+  <si>
+    <t>武器模型配对表</t>
   </si>
   <si>
     <t>运营相关</t>
@@ -525,7 +555,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -535,6 +565,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -851,7 +893,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -875,16 +917,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -896,96 +938,108 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1310,21 +1364,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="26.8333333333333" style="2" customWidth="1"/>
-    <col min="3" max="3" width="25.0833333333333" style="2" customWidth="1"/>
-    <col min="4" max="4" width="50.0833333333333" style="2" customWidth="1"/>
-    <col min="5" max="5" width="50.9166666666667" style="2" customWidth="1"/>
-    <col min="6" max="6" width="84.25" style="2" customWidth="1"/>
-    <col min="7" max="7" width="31.5" style="2" customWidth="1"/>
-    <col min="8" max="8" width="55.25" style="2" customWidth="1"/>
-    <col min="9" max="9" width="18" style="2" customWidth="1"/>
-    <col min="10" max="10" width="28.75" style="2" customWidth="1"/>
-    <col min="11" max="11" width="34.25" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="9" style="4"/>
+    <col min="2" max="2" width="26.8333333333333" style="4" customWidth="1"/>
+    <col min="3" max="3" width="25.0833333333333" style="4" customWidth="1"/>
+    <col min="4" max="4" width="50.0833333333333" style="4" customWidth="1"/>
+    <col min="5" max="5" width="50.9166666666667" style="4" customWidth="1"/>
+    <col min="6" max="6" width="84.25" style="4" customWidth="1"/>
+    <col min="7" max="7" width="31.5" style="4" customWidth="1"/>
+    <col min="8" max="8" width="55.25" style="4" customWidth="1"/>
+    <col min="9" max="9" width="18" style="4" customWidth="1"/>
+    <col min="10" max="10" width="28.75" style="4" customWidth="1"/>
+    <col min="11" max="11" width="34.25" style="4" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:11">
@@ -1418,381 +1472,430 @@
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="D4" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" s="3" t="s">
+      <c r="D5" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="4" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="D6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="2" t="s">
+      <c r="H6" s="5"/>
+      <c r="I6" s="4" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="D7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" s="3" t="s">
+      <c r="D8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="4" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3" t="s">
+      <c r="D9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="I9" s="4" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3" t="s">
+      <c r="D10" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="I10" s="4" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:11">
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" s="3" t="s">
+      <c r="D11" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="I11" s="4" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:11">
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D12" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" s="3" t="s">
+      <c r="D12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="I12" s="4" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3" t="s">
+      <c r="D13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="2" t="s">
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="4" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" s="3" t="s">
+      <c r="D14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="I14" s="4" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D15" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" s="3" t="s">
+      <c r="D15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="I15" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D16" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" s="3" t="s">
+      <c r="D16" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="I16" s="4" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:10">
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D17" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="3" t="s">
+      <c r="D17" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="I17" s="2" t="s">
+      <c r="I17" s="4" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="D18" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="3" t="s">
+      <c r="D18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="I18" s="2" t="s">
+      <c r="I18" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="J18" s="4" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="3" t="s">
+      <c r="B19" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="3" t="s">
+      <c r="B20" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D20" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" spans="1:10">
+      <c r="A21" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="B21" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D21" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="B22" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D22" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="2" t="s">
-        <v>98</v>
+    </row>
+    <row r="22" s="3" customFormat="1" spans="1:10">
+      <c r="A22" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:10">
-      <c r="B23" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="B23" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D23" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E23" s="3" t="s">
+      <c r="C23" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="I23" s="2" t="s">
+      <c r="D23" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="8" t="s">
         <v>102</v>
       </c>
+      <c r="H23" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D24" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="B25" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="H25" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D24" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="B25" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D25" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>110</v>
+      <c r="I25" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="B26" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D26" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="B27" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D27" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/GameConfig/Datas/Defines/__tables__.xlsx
+++ b/GameConfig/Datas/Defines/__tables__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub_Project\DGame_Fantasy\GameConfig\Datas\Defines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C731C3F-B043-4066-BBC7-018FD1651F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D9CCB86-0278-4CEB-893D-393231098549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="136">
   <si>
     <t>##var</t>
   </si>
@@ -168,9 +168,6 @@
   </si>
   <si>
     <t>SoundConfig</t>
-  </si>
-  <si>
-    <t>通用/音效配置表.xlsx</t>
   </si>
   <si>
     <t>音效配置表</t>
@@ -424,6 +421,33 @@
   </si>
   <si>
     <t>新手引导步骤配置表@通用/新手引导配置表.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>音效配置表@音效配置表.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbSoundRandomConfig</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SoundRandomConfig</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>音效随机配置表@音效配置表.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>音效随机配置表</t>
+  </si>
+  <si>
+    <t>group_by:SoundID</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -431,7 +455,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -448,6 +472,14 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -513,7 +545,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -792,7 +824,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
@@ -978,382 +1010,414 @@
         <v>1</v>
       </c>
       <c r="E8" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="I8" s="4" t="s">
-        <v>46</v>
-      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B9" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>48</v>
+      <c r="B9" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>131</v>
       </c>
       <c r="D9" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>49</v>
+        <v>132</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>50</v>
+        <v>133</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D10" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D11" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D12" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D13" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D14" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D15" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>74</v>
+        <v>68</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D16" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D17" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D18" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D19" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>94</v>
+        <v>86</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>121</v>
+        <v>88</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="D20" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="E20" s="5" t="s">
-        <v>128</v>
+      <c r="E20" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>92</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>123</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D21" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B22" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="D22" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="I22" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D21" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="I21" s="4" t="s">
+      <c r="J22" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="J21" s="4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B23" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="D23" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D22" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" s="4" t="s">
+      <c r="F23" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="I23" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="F22" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I22" s="4" t="s">
+    </row>
+    <row r="24" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>98</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B25" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D25" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D26" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>107</v>
+        <v>101</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>102</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D27" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D28" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B30" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="D30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="D29" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E29" s="4" t="s">
+      <c r="H30" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="I30" s="4" t="s">
         <v>119</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>120</v>
       </c>
     </row>
   </sheetData>
